--- a/apps/demo/public/samples/sales-table.xlsx
+++ b/apps/demo/public/samples/sales-table.xlsx
@@ -139,6 +139,23 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SalesRecords" displayName="SalesRecords" ref="A1:H181" headerRowCount="1">
+  <autoFilter ref="A1:H181"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Region"/>
+    <tableColumn id="2" name="Rep"/>
+    <tableColumn id="3" name="Product"/>
+    <tableColumn id="4" name="Month"/>
+    <tableColumn id="5" name="Units"/>
+    <tableColumn id="6" name="Unit Price"/>
+    <tableColumn id="7" name="Revenue"/>
+    <tableColumn id="8" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7147,5 +7164,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>